--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34C.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>46FFC97C5B5611E47191CD2E4A147A9B</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
   </si>
   <si>
     <t/>
@@ -136,22 +145,13 @@
     <t>Inventarios</t>
   </si>
   <si>
-    <t>515714274D0E2B84BAC2E79501DCE73C</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de enero del 2022 al 30 de Junio del 2022 el colegio de bachilleres del estado de tlaxcala no ha registrado ninguna baja de bienes muebles</t>
+    <t>17/01/2023</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero del 2023 al 30 de Julio del 2023 el Colegio de Bachilleres del Estado de Tlaxcala no ha registrado ninguna baja de bienes muebles</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="145.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="139.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -732,34 +732,34 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>43</v>
